--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1367,7 +1237,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -9843,7 +9713,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -9935,7 +9805,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -10671,7 +10541,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10901,7 +10771,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -12947,2449 +12817,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>柏蔚森 III - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>264 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>14 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>229 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>18 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$655万
-$24,894/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$746万
-$18,921/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$497万
-$19,042/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$499万
-$19,181/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$882万
-$22,603/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$524万
-$19,909/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$738万
-$18,736/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$495万
-$18,966/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$494万
-$18,988/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$716万
-$18,349/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$519万
-$19,719/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$734万
-$18,642/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$496万
-$18,996/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$486万
-$18,692/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$712万
-$18,259/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$511万
-$19,418/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$939万
-$24,520/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$871万
-$22,801/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$897万
-$22,701/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$731万
-$18,548/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$493万
-$18,900/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="K9" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$484万
-$18,600/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="L9" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$708万
-$18,167/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$506万
-$19,224/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$862万
-$22,496/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$843万
-$22,071/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$888万
-$22,476/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$727万
-$18,457/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$491万
-$18,805/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$481万
-$18,508/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$706万
-$18,113/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,964万
-$29,488/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$503万
-$19,125/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$885万
-$23,110/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$842万
-$22,050/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$838万
-$21,203/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$725万
-$18,404/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$488万
-$18,713/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K11" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$499万
-$19,208/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="L11" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$704万
-$18,056/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,514万
-$26,154/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$503万
-$19,137/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$812万
-$21,204/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$795万
-$20,801/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$813万
-$20,587/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$720万
-$18,277/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$486万
-$18,621/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$479万
-$18,427/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="L12" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$732万
-$18,772/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$990万
-$25,919/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,556万
-$26,870/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$498万
-$18,935/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$783万
-$20,446/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$769万
-$20,136/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$787万
-$19,929/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$718万
-$18,221/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$484万
-$18,529/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$477万
-$18,338/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L13" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$747万
-$19,156/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,698万
-$25,500/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,427万
-$24,653/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$496万
-$18,840/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$763万
-$19,927/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$747万
-$19,550/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$764万
-$19,347/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$749万
-$19,015/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$502万
-$19,222/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$474万
-$18,246/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$728万
-$18,662/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,756万
-$26,362/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,386万
-$23,934/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$496万
-$18,856/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$741万
-$19,347/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$725万
-$18,982/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$742万
-$18,787/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$716万
-$18,183/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$499万
-$19,126/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$600万
-$23,062/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$694万
-$17,800/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,626万
-$24,410/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$947万
-$24,788/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,352万
-$23,349/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$490万
-$18,650/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$703万
-$18,350/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$717万
-$18,772/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$704万
-$17,818/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$745万
-$18,901/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$476万
-$18,253/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$470万
-$18,065/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L16" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$687万
-$17,623/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,594万
-$23,932/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$906万
-$23,720/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,332万
-$23,005/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$488万
-$18,559/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$699万
-$18,261/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$684万
-$17,914/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$700万
-$17,729/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$712万
-$18,074/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J17" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$472万
-$18,073/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$465万
-$17,885/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="L17" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$710万
-$18,195/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,563万
-$23,462/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$867万
-$22,696/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,312万
-$22,665/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$486万
-$18,464/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$696万
-$18,170/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$681万
-$17,825/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$697万
-$17,641/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$710万
-$18,020/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$470万
-$18,019/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K18" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$464万
-$17,831/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L18" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$678万
-$17,397/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,532万
-$23,002/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$1,007万
-$26,361/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,247万
-$21,537/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$480万
-$18,232/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$692万
-$18,063/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$677万
-$17,712/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$693万
-$17,537/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$708万
-$17,967/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J19" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$469万
-$17,966/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K19" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$462万
-$17,781/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L19" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$705万
-$18,087/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,502万
-$22,550/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$838万
-$21,924/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,239万
-$21,404/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$477万
-$18,144/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$688万
-$17,971/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$673万
-$17,623/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$686万
-$17,377/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$706万
-$17,911/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$468万
-$17,912/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$461万
-$17,727/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L20" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$674万
-$17,290/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,470万
-$22,069/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$812万
-$21,254/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,218万
-$21,033/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$475万
-$18,053/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$685万
-$17,883/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$670万
-$17,534/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$686万
-$17,362/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$692万
-$17,561/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$458万
-$17,559/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$452万
-$17,381/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$670万
-$17,169/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,461万
-$21,932/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$808万
-$21,147/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,224万
-$21,149/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$472万
-$17,966/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$682万
-$17,794/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$666万
-$17,448/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$712万
-$18,015/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$707万
-$17,954/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$468万
-$17,946/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$443万
-$17,038/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$670万
-$17,187/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,426万
-$21,416/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$838万
-$21,940/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,216万
-$20,997/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$598万
-$22,745/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$680万
-$17,742/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$693万
-$18,136/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$680万
-$17,223/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$665万
-$16,878/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$440万
-$16,877/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$453万
-$17,415/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L23" s="19" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,418万
-$21,288/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$800万
-$20,937/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,212万
-$20,940/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$470万
-$17,856/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$706万
-$18,444/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$663万
-$17,346/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$676万
-$17,101/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$663万
-$16,830/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$439万
-$16,828/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$433万
-$16,654/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L24" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$666万
-$17,087/呎
-(24年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,464万
-$21,977/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$792万
-$20,730/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,200万
-$20,731/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$488万
-$18,567/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$675万
-$17,632/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$660万
-$17,291/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$674万
-$17,051/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$661万
-$16,779/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$438万
-$16,778/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K25" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$432万
-$16,604/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L25" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$664万
-$17,036/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,449万
-$21,761/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$784万
-$20,526/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,188万
-$20,527/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$467万
-$17,753/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$670万
-$17,507/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$656万
-$17,165/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$674万
-$17,068/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$659万
-$16,726/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$554万
-$21,245/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$449万
-$17,262/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L26" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$662万
-$16,985/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,383万
-$20,766/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$813万
-$21,293/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,183万
-$20,425/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$465万
-$17,696/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$671万
-$17,527/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$657万
-$17,188/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$672万
-$17,018/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$657万
-$16,678/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$435万
-$16,674/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$429万
-$16,504/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L27" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$660万
-$16,931/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 666呎 (3房)
-$1,363万
-$20,470/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 382呎 (2房)
-$776万
-$20,319/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,177万
-$20,323/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$464万
-$17,643/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$669万
-$17,475/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$655万
-$17,136/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$670万
-$16,967/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$642万
-$16,302/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>J | 261呎 (1房)
-$434万
-$16,625/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>K | 260呎 (1房)
-$427万
-$16,438/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$658万
-$16,882/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 628呎 (3房)
-$1,597万
-$25,428/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 344呎 (2房)
-$739万
-$21,494/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 579呎 (3房)
-$1,158万
-$20,000/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 263呎 (1房)
-$463万
-$17,589/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$654万
-$17,089/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 382呎 (2房)
-$648万
-$16,969/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>G | 395呎 (2房)
-$643万
-$16,271/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>H | 394呎 (2房)
-$640万
-$16,254/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>J | 224呎 (1房)
-$425万
-$18,960/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K29" s="18" t="inlineStr">
-        <is>
-          <t>K | 223呎 (1房)
-$438万
-$19,619/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="L29" s="18" t="inlineStr">
-        <is>
-          <t>L | 390呎 (2房)
-$656万
-$16,831/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +148,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -12817,4 +12996,2449 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$655万
+$24,894/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$746万
+$18,921/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$497万
+$19,042/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$499万
+$19,181/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$882万
+$22,603/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$524万
+$19,909/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$738万
+$18,736/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$495万
+$18,966/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$494万
+$18,988/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$716万
+$18,349/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$519万
+$19,719/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$734万
+$18,642/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$496万
+$18,996/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$486万
+$18,692/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="L7" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$712万
+$18,259/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$511万
+$19,418/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$939万
+$24,520/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$871万
+$22,801/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$897万
+$22,701/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$731万
+$18,548/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$493万
+$18,900/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$484万
+$18,600/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$708万
+$18,167/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$506万
+$19,224/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$862万
+$22,496/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$843万
+$22,071/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$888万
+$22,476/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$727万
+$18,457/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$491万
+$18,805/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$481万
+$18,508/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$706万
+$18,113/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1964万
+$29,488/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$503万
+$19,125/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$885万
+$23,110/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$842万
+$22,050/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$838万
+$21,203/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$725万
+$18,404/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$488万
+$18,713/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$499万
+$19,208/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$704万
+$18,056/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1514万
+$26,154/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$503万
+$19,137/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$812万
+$21,204/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$795万
+$20,801/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$813万
+$20,587/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$720万
+$18,277/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$486万
+$18,621/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$479万
+$18,427/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="L11" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$732万
+$18,772/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$990万
+$25,919/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1556万
+$26,870/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$498万
+$18,935/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$783万
+$20,446/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$769万
+$20,136/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$787万
+$19,929/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$718万
+$18,221/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$484万
+$18,529/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$477万
+$18,338/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$747万
+$19,156/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1698万
+$25,500/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1427万
+$24,653/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$496万
+$18,840/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$763万
+$19,927/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$747万
+$19,550/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$764万
+$19,347/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$749万
+$19,015/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$502万
+$19,222/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$474万
+$18,246/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$728万
+$18,662/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1756万
+$26,362/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1386万
+$23,934/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$496万
+$18,856/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$741万
+$19,347/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$725万
+$18,982/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$742万
+$18,787/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$716万
+$18,183/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$499万
+$19,126/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$600万
+$23,062/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$694万
+$17,800/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1626万
+$24,410/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$947万
+$24,788/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1352万
+$23,349/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$490万
+$18,650/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$703万
+$18,350/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$717万
+$18,772/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$704万
+$17,818/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$745万
+$18,901/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$476万
+$18,253/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$470万
+$18,065/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$687万
+$17,623/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1594万
+$23,932/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$906万
+$23,720/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1332万
+$23,005/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$488万
+$18,559/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$699万
+$18,261/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$684万
+$17,914/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$700万
+$17,729/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$712万
+$18,074/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$472万
+$18,073/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$465万
+$17,885/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$710万
+$18,195/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1563万
+$23,462/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$867万
+$22,696/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1312万
+$22,665/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$486万
+$18,464/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$696万
+$18,170/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$681万
+$17,825/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$697万
+$17,641/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$710万
+$18,020/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$470万
+$18,019/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$464万
+$17,831/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L17" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$678万
+$17,397/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1532万
+$23,002/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$1007万
+$26,361/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1247万
+$21,537/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$480万
+$18,232/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$692万
+$18,063/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$677万
+$17,712/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$693万
+$17,537/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$708万
+$17,967/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$469万
+$17,966/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$462万
+$17,781/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$705万
+$18,087/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1502万
+$22,550/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$838万
+$21,924/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1239万
+$21,404/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$477万
+$18,144/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$688万
+$17,971/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$673万
+$17,623/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$686万
+$17,377/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$706万
+$17,911/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$468万
+$17,912/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$461万
+$17,727/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$674万
+$17,290/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1470万
+$22,069/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$812万
+$21,254/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1218万
+$21,033/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$475万
+$18,053/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$685万
+$17,883/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$670万
+$17,534/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$686万
+$17,362/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$692万
+$17,561/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$458万
+$17,559/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$452万
+$17,381/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$670万
+$17,169/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1461万
+$21,932/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$808万
+$21,147/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1224万
+$21,149/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$472万
+$17,966/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$682万
+$17,794/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$666万
+$17,448/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$712万
+$18,015/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$707万
+$17,954/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$468万
+$17,946/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$443万
+$17,038/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$670万
+$17,187/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1426万
+$21,416/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$838万
+$21,940/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1216万
+$20,997/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$598万
+$22,745/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$680万
+$17,742/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$693万
+$18,136/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$680万
+$17,223/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$665万
+$16,878/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$440万
+$16,877/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$453万
+$17,415/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1418万
+$21,288/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$800万
+$20,937/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1212万
+$20,940/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$470万
+$17,856/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$706万
+$18,444/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$663万
+$17,346/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$676万
+$17,101/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$663万
+$16,830/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$439万
+$16,828/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$433万
+$16,654/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$666万
+$17,087/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1464万
+$21,977/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$792万
+$20,730/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1200万
+$20,731/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$488万
+$18,567/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$675万
+$17,632/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$660万
+$17,291/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$674万
+$17,051/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$661万
+$16,779/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$438万
+$16,778/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$432万
+$16,604/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$664万
+$17,036/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1449万
+$21,761/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$784万
+$20,526/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1188万
+$20,527/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$467万
+$17,753/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$670万
+$17,507/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$656万
+$17,165/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$674万
+$17,068/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$659万
+$16,726/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$554万
+$21,245/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$449万
+$17,262/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$662万
+$16,985/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1383万
+$20,766/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$813万
+$21,293/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1183万
+$20,425/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$465万
+$17,696/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$671万
+$17,527/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$657万
+$17,188/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$672万
+$17,018/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$657万
+$16,678/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$435万
+$16,674/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$429万
+$16,504/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$660万
+$16,931/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 666呎 (3房)
+$1363万
+$20,470/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 382呎 (2房)
+$776万
+$20,319/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1177万
+$20,323/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$464万
+$17,643/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$669万
+$17,475/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$655万
+$17,136/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$670万
+$16,967/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$642万
+$16,302/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>J | 261呎 (1房)
+$434万
+$16,625/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>K | 260呎 (1房)
+$427万
+$16,438/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="L27" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$658万
+$16,882/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 628呎 (3房)
+$1597万
+$25,428/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 344呎 (2房)
+$739万
+$21,494/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 579呎 (3房)
+$1158万
+$20,000/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 263呎 (1房)
+$463万
+$17,589/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$654万
+$17,089/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 382呎 (2房)
+$648万
+$16,969/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 395呎 (2房)
+$643万
+$16,271/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 394呎 (2房)
+$640万
+$16,254/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>J | 224呎 (1房)
+$425万
+$18,960/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>K | 223呎 (1房)
+$438万
+$19,619/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>L | 390呎 (2房)
+$656万
+$16,831/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -14804,7 +14804,7 @@
           <t>D | 263呎 (1房)
 $598万
 $22,745/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J266"/>
+  <dimension ref="A1:N266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -759,6 +783,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>7228300</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>18534</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -805,6 +845,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>4987000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>19181</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -851,6 +907,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>4970000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>19042</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -897,6 +969,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>7455000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>18921</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -947,6 +1035,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -997,6 +1105,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1047,6 +1175,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1093,6 +1241,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5368540</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>20413</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1143,6 +1307,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1193,6 +1377,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1243,6 +1447,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1289,6 +1513,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7156000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>18349</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1335,6 +1575,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>4937000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>18988</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1381,6 +1637,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>4950000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>18966</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1427,6 +1699,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>7382000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>18736</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1477,6 +1765,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1527,6 +1835,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1577,6 +1905,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1623,6 +1971,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>5236000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>19909</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1673,6 +2037,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1723,6 +2107,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1773,6 +2177,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1819,6 +2243,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>7121000</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>18259</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1865,6 +2305,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>4860000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>18692</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1911,6 +2367,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>4958000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>18996</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1957,6 +2429,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>7345000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>18642</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2007,6 +2495,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2057,6 +2565,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2107,6 +2635,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2153,6 +2701,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>5186000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>19719</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2203,6 +2767,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2253,6 +2837,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2303,6 +2907,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2349,6 +2973,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>7085000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>18167</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2395,6 +3035,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>4836000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>18600</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2441,6 +3097,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>4933000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>18900</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2487,6 +3159,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>7308000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>18548</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2533,6 +3221,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>8967000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>22701</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2579,6 +3283,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>8710000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>22801</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2625,6 +3345,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>9391000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>24520</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2671,6 +3407,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>5107000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>19418</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2721,6 +3473,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2771,6 +3543,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2821,6 +3613,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2867,6 +3679,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>7064000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>18113</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2913,6 +3741,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>4812000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>18508</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2959,6 +3803,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>4908000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>18805</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3005,6 +3865,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>7272000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>18457</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3051,6 +3927,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>8878000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>22476</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3097,6 +3989,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>8431000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>22071</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3143,6 +4051,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>8616000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>22496</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3189,6 +4113,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>5056000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>19224</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3239,6 +4179,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3289,6 +4249,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3339,6 +4319,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3385,6 +4385,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>7042000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>18056</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3431,6 +4447,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>4994000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>19208</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3477,6 +4509,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>4884000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>18713</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3523,6 +4571,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>7251000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>18404</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3569,6 +4633,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>8375000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>21203</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3615,6 +4695,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>8423000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>22050</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3661,6 +4757,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>8851000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>23110</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3707,6 +4819,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>5030000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>19125</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3757,6 +4885,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3807,6 +4955,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3853,6 +5021,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>19639000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>29488</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3899,6 +5083,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>7321000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>18772</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3945,6 +5145,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>4791000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>18427</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3991,6 +5207,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>4860000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>18621</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4037,6 +5269,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>7201000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>18277</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4083,6 +5331,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>8132000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>20587</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4129,6 +5393,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>7946000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>20801</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4175,6 +5455,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>8121000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>21204</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4221,6 +5517,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>5033000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>19137</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4267,6 +5579,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>15143000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>26154</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4317,6 +5645,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4367,6 +5715,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4413,6 +5781,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>7471000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>19156</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4459,6 +5843,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>4768000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>18338</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4505,6 +5905,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>4836000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>18529</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4551,6 +5967,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>7179000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>18221</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4597,6 +6029,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>7872000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>19929</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4643,6 +6091,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>7692000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>20136</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4689,6 +6153,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>7831000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>20446</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4735,6 +6215,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>4980000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>18935</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4781,6 +6277,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>15558000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>26870</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4827,6 +6339,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>9901000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>25919</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4877,6 +6405,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4923,6 +6471,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>7278000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>18662</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4969,6 +6533,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>4744000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>18246</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5015,6 +6595,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>5017000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>19222</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5061,6 +6657,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>7492000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>19015</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5107,6 +6719,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>7642000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>19347</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5153,6 +6781,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>7468000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>19550</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5199,6 +6843,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>7632000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>19927</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5245,6 +6905,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>4955000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>18840</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5291,6 +6967,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>14274000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>24653</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5341,6 +7033,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5387,6 +7099,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>16983000</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>25500</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5433,6 +7161,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>6942000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>17800</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5479,6 +7223,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>5996000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>23062</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5525,6 +7285,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>4992000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>19126</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5571,6 +7347,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>7164000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>18183</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5617,6 +7409,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>7421000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>18787</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5663,6 +7471,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>7251000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>18982</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5709,6 +7533,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>7410000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>19347</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5755,6 +7595,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>4959000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>18856</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5801,6 +7657,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>13858000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>23934</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5851,6 +7723,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5897,6 +7789,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>17557000</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>26362</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5943,6 +7851,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>6873000</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>17623</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5989,6 +7913,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>4697000</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>18065</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6035,6 +7975,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>4764000</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>18253</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6081,6 +8037,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>7447000</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>18901</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6127,6 +8099,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>7038000</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>17818</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6173,6 +8161,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>7171000</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>18772</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6219,6 +8223,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>7028000</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>18350</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6265,6 +8285,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>4905000</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>18650</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6311,6 +8347,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>13519000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>23349</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6357,6 +8409,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>9469000</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>24788</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6403,6 +8471,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>16257000</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>24410</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6449,6 +8533,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>7096000</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>18195</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6495,6 +8595,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>17885</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6541,6 +8657,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>4717000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>18073</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6587,6 +8719,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>7121000</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>18074</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6633,6 +8781,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>7003000</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>17729</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6679,6 +8843,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>6843000</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>17914</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6725,6 +8905,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>6994000</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>18261</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6771,6 +8967,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>4881000</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>18559</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6817,6 +9029,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>13320000</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>23005</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6863,6 +9091,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>9061000</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>23720</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6909,6 +9153,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>15939000</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>23932</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6955,6 +9215,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>6785000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>17397</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7001,6 +9277,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>4636000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>17831</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7047,6 +9339,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>4703000</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>18019</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7093,6 +9401,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>7100000</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>18020</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7139,6 +9463,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>6968000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>17641</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7185,6 +9525,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>6809000</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>17825</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7231,6 +9587,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>6959000</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>18170</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7277,6 +9649,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>4856000</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>18464</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7323,6 +9711,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>13123000</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>22665</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7369,6 +9773,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>8670000</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>22696</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7415,6 +9835,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>15626000</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>23462</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7461,6 +9897,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>7054000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>18087</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7507,6 +9959,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>4623000</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>17781</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7553,6 +10021,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>4689000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>17966</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7599,6 +10083,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>7079000</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>17967</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7645,6 +10145,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>6927000</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>17537</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7691,6 +10207,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>6766000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>17712</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7737,6 +10269,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>6918000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>18063</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7783,6 +10331,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>4795000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>18232</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7829,6 +10393,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>12470000</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>21537</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7875,6 +10455,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>8257400</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>21616</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7921,6 +10517,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>15319000</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>23002</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7967,6 +10579,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>6743000</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>17290</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8013,6 +10641,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>4609000</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>17727</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8059,6 +10703,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>4675000</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>17912</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8105,6 +10765,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>7057000</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>17911</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8151,6 +10827,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>6864000</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>17377</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8197,6 +10889,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>6732000</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>17623</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8243,6 +10951,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>6883000</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>17971</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8289,6 +11013,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>4772000</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>18144</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8335,6 +11075,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>12393000</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>21404</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8381,6 +11137,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>8375000</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>21924</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8427,6 +11199,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>15018000</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>22550</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8473,6 +11261,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>6696000</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>17169</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8519,6 +11323,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>4519000</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>17381</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8565,6 +11385,22 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>4583000</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>17559</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8611,6 +11447,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>6919000</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>17561</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8657,6 +11509,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>6858000</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>17362</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8703,6 +11571,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>6698000</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>17534</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8749,6 +11633,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>6849000</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>17883</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8795,6 +11695,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>4748000</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>18053</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8841,6 +11757,22 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>12178000</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>21033</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8887,6 +11819,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>8119000</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>21254</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8933,6 +11881,22 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>14698000</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>22069</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8979,6 +11943,22 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>6703000</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>17187</v>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9025,6 +12005,22 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>4430000</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>17038</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9071,6 +12067,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>4684000</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>17946</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9117,6 +12129,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>7074000</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>17954</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9163,6 +12191,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>7116000</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>18015</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9209,6 +12253,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>6665000</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>17448</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9255,6 +12315,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>6815000</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>17794</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9301,6 +12377,22 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>4725000</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>17966</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9347,6 +12439,22 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>12245000</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>21149</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9393,6 +12501,22 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>8078000</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>21147</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9439,6 +12563,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>14607000</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>21932</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9489,6 +12629,26 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9535,6 +12695,22 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>4528000</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>17415</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9581,6 +12757,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>4405000</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>16877</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9627,6 +12819,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>6650000</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>16878</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9673,6 +12881,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>6803000</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>17223</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9719,6 +12943,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>6928000</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>18136</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9765,6 +13005,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>6795000</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>17742</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9811,6 +13067,22 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>5982000</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>22745</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9857,6 +13129,22 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>12157000</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>20997</v>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9903,6 +13191,22 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>8381000</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>21940</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9949,6 +13253,22 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>14263000</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>21416</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9995,6 +13315,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>6664000</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>17087</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10041,6 +13377,22 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>4330000</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>16654</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10087,6 +13439,22 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>4392000</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>16828</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10133,6 +13501,22 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>6631000</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>16830</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10179,6 +13563,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>6755000</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>17101</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10225,6 +13625,22 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>6626000</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>17346</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10271,6 +13687,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>7064000</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>18444</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10317,6 +13749,22 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>4696000</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>17856</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10363,6 +13811,22 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>12124000</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>20940</v>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10409,6 +13873,22 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>7998000</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>20937</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10455,6 +13935,22 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>14178000</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>21288</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10501,6 +13997,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>6644000</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>17036</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10547,6 +14059,22 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>4317000</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>16604</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10593,6 +14121,22 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>4379000</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>16778</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10639,6 +14183,22 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>6611000</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>16779</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10685,6 +14245,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>6735000</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>17051</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10731,6 +14307,22 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>6605000</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>17291</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10777,6 +14369,22 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>6753000</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>17632</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10823,6 +14431,22 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>4883000</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>18567</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10869,6 +14493,22 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>12003000</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>20731</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10915,6 +14555,22 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>7919000</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>20730</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10961,6 +14617,22 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>14637000</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>21977</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11007,6 +14679,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>6624000</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>16985</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11053,6 +14741,22 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>4488000</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>17262</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11099,6 +14803,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>5545000</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>21245</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11145,6 +14865,22 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>6590000</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>16726</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11191,6 +14927,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>6742000</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>17068</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11237,6 +14989,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>6557000</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>17165</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11283,6 +15051,22 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>6705000</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>17507</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11329,6 +15113,22 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>4669000</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>17753</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11375,6 +15175,22 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>11885000</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>20527</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11421,6 +15237,22 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>7841000</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>20526</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11467,6 +15299,22 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>14493000</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>21761</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11513,6 +15361,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>6603000</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>16931</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11559,6 +15423,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>4291000</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>16504</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11605,6 +15485,22 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>4352000</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>16674</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11651,6 +15547,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>6571000</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>16678</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11697,6 +15609,22 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>6722000</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>17018</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11743,6 +15671,22 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>6566000</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>17188</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11789,6 +15733,22 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>6713000</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>17527</v>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11835,6 +15795,22 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>4654000</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>17696</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11881,6 +15857,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>11826000</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>20425</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11927,6 +15919,22 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>8134000</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>21293</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11973,6 +15981,22 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>13830000</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>20766</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12019,6 +16043,22 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>6584000</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>16882</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12065,6 +16105,22 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>4274000</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>16438</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12111,6 +16167,22 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>4339000</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>16625</v>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12157,6 +16229,22 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>6423000</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>16302</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12203,6 +16291,22 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>6702000</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>16967</v>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12249,6 +16353,22 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>6546000</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>17136</v>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12295,6 +16415,22 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>6693000</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>17475</v>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12341,6 +16477,22 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>4640000</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>17643</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12387,6 +16539,22 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>11767000</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>20323</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12433,6 +16601,22 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>7762000</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>20319</v>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12479,6 +16663,22 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>13633000</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>20470</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12525,6 +16725,22 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>6564000</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>16831</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12571,6 +16787,22 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>4375000</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>19619</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12617,6 +16849,22 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>4247000</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>18960</v>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12663,6 +16911,22 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>6404000</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>16254</v>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12709,6 +16973,22 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>6427000</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>16271</v>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12755,6 +17035,22 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>6482000</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>16969</v>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12801,6 +17097,22 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>6545000</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>17089</v>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12847,6 +17159,22 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>4626000</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>17589</v>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12893,6 +17221,22 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12939,6 +17283,22 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>7394000</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>21494</v>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12985,13 +17345,29 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>15969000</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>25428</v>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -13221,7 +17597,7 @@
           <t>H | 394呎 (2房)
 $746万
 $18,921/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -13229,7 +17605,7 @@
           <t>J | 261呎 (1房)
 $497万
 $19,042/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -13237,7 +17613,7 @@
           <t>K | 260呎 (1房)
 $499万
 $19,181/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -13284,7 +17660,7 @@
           <t>D | 263呎 (1房)
 $524万
 $19,909/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -13316,7 +17692,7 @@
           <t>H | 394呎 (2房)
 $738万
 $18,736/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -13324,7 +17700,7 @@
           <t>J | 261呎 (1房)
 $495万
 $18,966/呎
-(24年-09月)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -13332,7 +17708,7 @@
           <t>K | 260呎 (1房)
 $494万
 $18,988/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
@@ -13340,7 +17716,7 @@
           <t>L | 390呎 (2房)
 $716万
 $18,349/呎
-(24年-08月)</t>
+(24年-08月-18日)</t>
         </is>
       </c>
     </row>
@@ -13379,7 +17755,7 @@
           <t>D | 263呎 (1房)
 $519万
 $19,719/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -13411,7 +17787,7 @@
           <t>H | 394呎 (2房)
 $734万
 $18,642/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -13419,7 +17795,7 @@
           <t>J | 261呎 (1房)
 $496万
 $18,996/呎
-(24年-09月)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -13427,7 +17803,7 @@
           <t>K | 260呎 (1房)
 $486万
 $18,692/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -13435,7 +17811,7 @@
           <t>L | 390呎 (2房)
 $712万
 $18,259/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -13474,7 +17850,7 @@
           <t>D | 263呎 (1房)
 $511万
 $19,418/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -13482,7 +17858,7 @@
           <t>E | 383呎 (2房)
 $939万
 $24,520/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -13490,7 +17866,7 @@
           <t>F | 382呎 (2房)
 $871万
 $22,801/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -13498,7 +17874,7 @@
           <t>G | 395呎 (2房)
 $897万
 $22,701/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -13506,7 +17882,7 @@
           <t>H | 394呎 (2房)
 $731万
 $18,548/呎
-(24年-09月)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -13514,7 +17890,7 @@
           <t>J | 261呎 (1房)
 $493万
 $18,900/呎
-(24年-09月)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -13522,7 +17898,7 @@
           <t>K | 260呎 (1房)
 $484万
 $18,600/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -13530,7 +17906,7 @@
           <t>L | 390呎 (2房)
 $708万
 $18,167/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -13569,7 +17945,7 @@
           <t>D | 263呎 (1房)
 $506万
 $19,224/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -13577,7 +17953,7 @@
           <t>E | 383呎 (2房)
 $862万
 $22,496/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -13585,7 +17961,7 @@
           <t>F | 382呎 (2房)
 $843万
 $22,071/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -13593,7 +17969,7 @@
           <t>G | 395呎 (2房)
 $888万
 $22,476/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -13601,7 +17977,7 @@
           <t>H | 394呎 (2房)
 $727万
 $18,457/呎
-(24年-08月)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -13609,7 +17985,7 @@
           <t>J | 261呎 (1房)
 $491万
 $18,805/呎
-(24年-09月)</t>
+(24年-09月-08日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -13617,7 +17993,7 @@
           <t>K | 260呎 (1房)
 $481万
 $18,508/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
@@ -13625,7 +18001,7 @@
           <t>L | 390呎 (2房)
 $706万
 $18,113/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -13640,7 +18016,7 @@
           <t>A | 666呎 (3房)
 $1964万
 $29,488/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -13664,7 +18040,7 @@
           <t>D | 263呎 (1房)
 $503万
 $19,125/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -13672,7 +18048,7 @@
           <t>E | 383呎 (2房)
 $885万
 $23,110/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -13680,7 +18056,7 @@
           <t>F | 382呎 (2房)
 $842万
 $22,050/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -13688,7 +18064,7 @@
           <t>G | 395呎 (2房)
 $838万
 $21,203/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -13696,7 +18072,7 @@
           <t>H | 394呎 (2房)
 $725万
 $18,404/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -13704,7 +18080,7 @@
           <t>J | 261呎 (1房)
 $488万
 $18,713/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -13712,7 +18088,7 @@
           <t>K | 260呎 (1房)
 $499万
 $19,208/呎
-(24年-09月)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
@@ -13720,7 +18096,7 @@
           <t>L | 390呎 (2房)
 $704万
 $18,056/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -13751,7 +18127,7 @@
           <t>C | 579呎 (3房)
 $1514万
 $26,154/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -13759,7 +18135,7 @@
           <t>D | 263呎 (1房)
 $503万
 $19,137/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -13767,7 +18143,7 @@
           <t>E | 383呎 (2房)
 $812万
 $21,204/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -13775,7 +18151,7 @@
           <t>F | 382呎 (2房)
 $795万
 $20,801/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -13783,7 +18159,7 @@
           <t>G | 395呎 (2房)
 $813万
 $20,587/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -13791,7 +18167,7 @@
           <t>H | 394呎 (2房)
 $720万
 $18,277/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -13799,7 +18175,7 @@
           <t>J | 261呎 (1房)
 $486万
 $18,621/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -13807,7 +18183,7 @@
           <t>K | 260呎 (1房)
 $479万
 $18,427/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -13815,7 +18191,7 @@
           <t>L | 390呎 (2房)
 $732万
 $18,772/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -13838,7 +18214,7 @@
           <t>B | 382呎 (2房)
 $990万
 $25,919/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -13846,7 +18222,7 @@
           <t>C | 579呎 (3房)
 $1556万
 $26,870/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -13854,7 +18230,7 @@
           <t>D | 263呎 (1房)
 $498万
 $18,935/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -13862,7 +18238,7 @@
           <t>E | 383呎 (2房)
 $783万
 $20,446/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -13870,7 +18246,7 @@
           <t>F | 382呎 (2房)
 $769万
 $20,136/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -13878,7 +18254,7 @@
           <t>G | 395呎 (2房)
 $787万
 $19,929/呎
-(25年-10月)</t>
+(25年-10月-26日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -13886,7 +18262,7 @@
           <t>H | 394呎 (2房)
 $718万
 $18,221/呎
-(24年-10月)</t>
+(24年-10月-13日)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -13894,7 +18270,7 @@
           <t>J | 261呎 (1房)
 $484万
 $18,529/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -13902,7 +18278,7 @@
           <t>K | 260呎 (1房)
 $477万
 $18,338/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
@@ -13910,7 +18286,7 @@
           <t>L | 390呎 (2房)
 $747万
 $19,156/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -13925,7 +18301,7 @@
           <t>A | 666呎 (3房)
 $1698万
 $25,500/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -13941,7 +18317,7 @@
           <t>C | 579呎 (3房)
 $1427万
 $24,653/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -13949,7 +18325,7 @@
           <t>D | 263呎 (1房)
 $496万
 $18,840/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -13957,7 +18333,7 @@
           <t>E | 383呎 (2房)
 $763万
 $19,927/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -13965,7 +18341,7 @@
           <t>F | 382呎 (2房)
 $747万
 $19,550/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -13973,7 +18349,7 @@
           <t>G | 395呎 (2房)
 $764万
 $19,347/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -13981,7 +18357,7 @@
           <t>H | 394呎 (2房)
 $749万
 $19,015/呎
-(24年-08月)</t>
+(24年-08月-27日)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -13989,7 +18365,7 @@
           <t>J | 261呎 (1房)
 $502万
 $19,222/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -13997,7 +18373,7 @@
           <t>K | 260呎 (1房)
 $474万
 $18,246/呎
-(24年-09月)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr">
@@ -14005,7 +18381,7 @@
           <t>L | 390呎 (2房)
 $728万
 $18,662/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -14020,7 +18396,7 @@
           <t>A | 666呎 (3房)
 $1756万
 $26,362/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -14036,7 +18412,7 @@
           <t>C | 579呎 (3房)
 $1386万
 $23,934/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -14044,7 +18420,7 @@
           <t>D | 263呎 (1房)
 $496万
 $18,856/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -14052,7 +18428,7 @@
           <t>E | 383呎 (2房)
 $741万
 $19,347/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -14060,7 +18436,7 @@
           <t>F | 382呎 (2房)
 $725万
 $18,982/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -14068,7 +18444,7 @@
           <t>G | 395呎 (2房)
 $742万
 $18,787/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -14076,7 +18452,7 @@
           <t>H | 394呎 (2房)
 $716万
 $18,183/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -14084,7 +18460,7 @@
           <t>J | 261呎 (1房)
 $499万
 $19,126/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -14092,7 +18468,7 @@
           <t>K | 260呎 (1房)
 $600万
 $23,062/呎
-(26年-06月)</t>
+(26年-06月-19日)</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
@@ -14100,7 +18476,7 @@
           <t>L | 390呎 (2房)
 $694万
 $17,800/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -14115,7 +18491,7 @@
           <t>A | 666呎 (3房)
 $1626万
 $24,410/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -14123,7 +18499,7 @@
           <t>B | 382呎 (2房)
 $947万
 $24,788/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -14131,7 +18507,7 @@
           <t>C | 579呎 (3房)
 $1352万
 $23,349/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -14139,7 +18515,7 @@
           <t>D | 263呎 (1房)
 $490万
 $18,650/呎
-(24年-10月)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -14147,7 +18523,7 @@
           <t>E | 383呎 (2房)
 $703万
 $18,350/呎
-(24年-10月)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -14155,7 +18531,7 @@
           <t>F | 382呎 (2房)
 $717万
 $18,772/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -14163,7 +18539,7 @@
           <t>G | 395呎 (2房)
 $704万
 $17,818/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -14171,7 +18547,7 @@
           <t>H | 394呎 (2房)
 $745万
 $18,901/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -14179,7 +18555,7 @@
           <t>J | 261呎 (1房)
 $476万
 $18,253/呎
-(25年-02月)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -14187,7 +18563,7 @@
           <t>K | 260呎 (1房)
 $470万
 $18,065/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -14195,7 +18571,7 @@
           <t>L | 390呎 (2房)
 $687万
 $17,623/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -14210,7 +18586,7 @@
           <t>A | 666呎 (3房)
 $1594万
 $23,932/呎
-(26年-02月)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -14218,7 +18594,7 @@
           <t>B | 382呎 (2房)
 $906万
 $23,720/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -14226,7 +18602,7 @@
           <t>C | 579呎 (3房)
 $1332万
 $23,005/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -14234,7 +18610,7 @@
           <t>D | 263呎 (1房)
 $488万
 $18,559/呎
-(24年-10月)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -14242,7 +18618,7 @@
           <t>E | 383呎 (2房)
 $699万
 $18,261/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -14250,7 +18626,7 @@
           <t>F | 382呎 (2房)
 $684万
 $17,914/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -14258,7 +18634,7 @@
           <t>G | 395呎 (2房)
 $700万
 $17,729/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -14266,7 +18642,7 @@
           <t>H | 394呎 (2房)
 $712万
 $18,074/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -14274,7 +18650,7 @@
           <t>J | 261呎 (1房)
 $472万
 $18,073/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -14282,7 +18658,7 @@
           <t>K | 260呎 (1房)
 $465万
 $17,885/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -14290,7 +18666,7 @@
           <t>L | 390呎 (2房)
 $710万
 $18,195/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -14305,7 +18681,7 @@
           <t>A | 666呎 (3房)
 $1563万
 $23,462/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -14313,7 +18689,7 @@
           <t>B | 382呎 (2房)
 $867万
 $22,696/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -14321,7 +18697,7 @@
           <t>C | 579呎 (3房)
 $1312万
 $22,665/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -14329,7 +18705,7 @@
           <t>D | 263呎 (1房)
 $486万
 $18,464/呎
-(24年-10月)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -14337,7 +18713,7 @@
           <t>E | 383呎 (2房)
 $696万
 $18,170/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -14345,7 +18721,7 @@
           <t>F | 382呎 (2房)
 $681万
 $17,825/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -14353,7 +18729,7 @@
           <t>G | 395呎 (2房)
 $697万
 $17,641/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -14361,7 +18737,7 @@
           <t>H | 394呎 (2房)
 $710万
 $18,020/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -14369,7 +18745,7 @@
           <t>J | 261呎 (1房)
 $470万
 $18,019/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -14377,7 +18753,7 @@
           <t>K | 260呎 (1房)
 $464万
 $17,831/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -14385,7 +18761,7 @@
           <t>L | 390呎 (2房)
 $678万
 $17,397/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -14400,7 +18776,7 @@
           <t>A | 666呎 (3房)
 $1532万
 $23,002/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -14416,7 +18792,7 @@
           <t>C | 579呎 (3房)
 $1247万
 $21,537/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -14424,7 +18800,7 @@
           <t>D | 263呎 (1房)
 $480万
 $18,232/呎
-(24年-08月)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -14432,7 +18808,7 @@
           <t>E | 383呎 (2房)
 $692万
 $18,063/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -14440,7 +18816,7 @@
           <t>F | 382呎 (2房)
 $677万
 $17,712/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -14448,7 +18824,7 @@
           <t>G | 395呎 (2房)
 $693万
 $17,537/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -14456,7 +18832,7 @@
           <t>H | 394呎 (2房)
 $708万
 $17,967/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -14464,7 +18840,7 @@
           <t>J | 261呎 (1房)
 $469万
 $17,966/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -14472,7 +18848,7 @@
           <t>K | 260呎 (1房)
 $462万
 $17,781/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -14480,7 +18856,7 @@
           <t>L | 390呎 (2房)
 $705万
 $18,087/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -14495,7 +18871,7 @@
           <t>A | 666呎 (3房)
 $1502万
 $22,550/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -14503,7 +18879,7 @@
           <t>B | 382呎 (2房)
 $838万
 $21,924/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -14511,7 +18887,7 @@
           <t>C | 579呎 (3房)
 $1239万
 $21,404/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -14519,7 +18895,7 @@
           <t>D | 263呎 (1房)
 $477万
 $18,144/呎
-(24年-09月)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -14527,7 +18903,7 @@
           <t>E | 383呎 (2房)
 $688万
 $17,971/呎
-(24年-09月)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -14535,7 +18911,7 @@
           <t>F | 382呎 (2房)
 $673万
 $17,623/呎
-(24年-08月)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -14543,7 +18919,7 @@
           <t>G | 395呎 (2房)
 $686万
 $17,377/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -14551,7 +18927,7 @@
           <t>H | 394呎 (2房)
 $706万
 $17,911/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -14559,7 +18935,7 @@
           <t>J | 261呎 (1房)
 $468万
 $17,912/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -14567,7 +18943,7 @@
           <t>K | 260呎 (1房)
 $461万
 $17,727/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -14575,7 +18951,7 @@
           <t>L | 390呎 (2房)
 $674万
 $17,290/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -14590,7 +18966,7 @@
           <t>A | 666呎 (3房)
 $1470万
 $22,069/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -14598,7 +18974,7 @@
           <t>B | 382呎 (2房)
 $812万
 $21,254/呎
-(24年-08月)</t>
+(24年-08月-18日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -14606,7 +18982,7 @@
           <t>C | 579呎 (3房)
 $1218万
 $21,033/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -14614,7 +18990,7 @@
           <t>D | 263呎 (1房)
 $475万
 $18,053/呎
-(24年-09月)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -14622,7 +18998,7 @@
           <t>E | 383呎 (2房)
 $685万
 $17,883/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -14630,7 +19006,7 @@
           <t>F | 382呎 (2房)
 $670万
 $17,534/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -14638,7 +19014,7 @@
           <t>G | 395呎 (2房)
 $686万
 $17,362/呎
-(24年-09月)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -14646,7 +19022,7 @@
           <t>H | 394呎 (2房)
 $692万
 $17,561/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -14654,7 +19030,7 @@
           <t>J | 261呎 (1房)
 $458万
 $17,559/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -14662,7 +19038,7 @@
           <t>K | 260呎 (1房)
 $452万
 $17,381/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -14670,7 +19046,7 @@
           <t>L | 390呎 (2房)
 $670万
 $17,169/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -14685,7 +19061,7 @@
           <t>A | 666呎 (3房)
 $1461万
 $21,932/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -14693,7 +19069,7 @@
           <t>B | 382呎 (2房)
 $808万
 $21,147/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -14701,7 +19077,7 @@
           <t>C | 579呎 (3房)
 $1224万
 $21,149/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -14709,7 +19085,7 @@
           <t>D | 263呎 (1房)
 $472万
 $17,966/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -14717,7 +19093,7 @@
           <t>E | 383呎 (2房)
 $682万
 $17,794/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -14725,7 +19101,7 @@
           <t>F | 382呎 (2房)
 $666万
 $17,448/呎
-(24年-08月)</t>
+(24年-08月-18日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -14733,7 +19109,7 @@
           <t>G | 395呎 (2房)
 $712万
 $18,015/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -14741,7 +19117,7 @@
           <t>H | 394呎 (2房)
 $707万
 $17,954/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -14749,7 +19125,7 @@
           <t>J | 261呎 (1房)
 $468万
 $17,946/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -14757,7 +19133,7 @@
           <t>K | 260呎 (1房)
 $443万
 $17,038/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -14765,7 +19141,7 @@
           <t>L | 390呎 (2房)
 $670万
 $17,187/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -14780,7 +19156,7 @@
           <t>A | 666呎 (3房)
 $1426万
 $21,416/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -14788,7 +19164,7 @@
           <t>B | 382呎 (2房)
 $838万
 $21,940/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -14796,7 +19172,7 @@
           <t>C | 579呎 (3房)
 $1216万
 $20,997/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -14804,7 +19180,7 @@
           <t>D | 263呎 (1房)
 $598万
 $22,745/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -14812,7 +19188,7 @@
           <t>E | 383呎 (2房)
 $680万
 $17,742/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -14820,7 +19196,7 @@
           <t>F | 382呎 (2房)
 $693万
 $18,136/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -14828,7 +19204,7 @@
           <t>G | 395呎 (2房)
 $680万
 $17,223/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -14836,7 +19212,7 @@
           <t>H | 394呎 (2房)
 $665万
 $16,878/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -14844,7 +19220,7 @@
           <t>J | 261呎 (1房)
 $440万
 $16,877/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -14852,7 +19228,7 @@
           <t>K | 260呎 (1房)
 $453万
 $17,415/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
@@ -14875,7 +19251,7 @@
           <t>A | 666呎 (3房)
 $1418万
 $21,288/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -14883,7 +19259,7 @@
           <t>B | 382呎 (2房)
 $800万
 $20,937/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -14891,7 +19267,7 @@
           <t>C | 579呎 (3房)
 $1212万
 $20,940/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -14899,7 +19275,7 @@
           <t>D | 263呎 (1房)
 $470万
 $17,856/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -14907,7 +19283,7 @@
           <t>E | 383呎 (2房)
 $706万
 $18,444/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -14915,7 +19291,7 @@
           <t>F | 382呎 (2房)
 $663万
 $17,346/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -14923,7 +19299,7 @@
           <t>G | 395呎 (2房)
 $676万
 $17,101/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -14931,7 +19307,7 @@
           <t>H | 394呎 (2房)
 $663万
 $16,830/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -14939,7 +19315,7 @@
           <t>J | 261呎 (1房)
 $439万
 $16,828/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -14947,7 +19323,7 @@
           <t>K | 260呎 (1房)
 $433万
 $16,654/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -14955,7 +19331,7 @@
           <t>L | 390呎 (2房)
 $666万
 $17,087/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -14970,7 +19346,7 @@
           <t>A | 666呎 (3房)
 $1464万
 $21,977/呎
-(24年-08月)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -14978,7 +19354,7 @@
           <t>B | 382呎 (2房)
 $792万
 $20,730/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -14986,7 +19362,7 @@
           <t>C | 579呎 (3房)
 $1200万
 $20,731/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -14994,7 +19370,7 @@
           <t>D | 263呎 (1房)
 $488万
 $18,567/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -15002,7 +19378,7 @@
           <t>E | 383呎 (2房)
 $675万
 $17,632/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -15010,7 +19386,7 @@
           <t>F | 382呎 (2房)
 $660万
 $17,291/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -15018,7 +19394,7 @@
           <t>G | 395呎 (2房)
 $674万
 $17,051/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -15026,7 +19402,7 @@
           <t>H | 394呎 (2房)
 $661万
 $16,779/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -15034,7 +19410,7 @@
           <t>J | 261呎 (1房)
 $438万
 $16,778/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -15042,7 +19418,7 @@
           <t>K | 260呎 (1房)
 $432万
 $16,604/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -15050,7 +19426,7 @@
           <t>L | 390呎 (2房)
 $664万
 $17,036/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -15065,7 +19441,7 @@
           <t>A | 666呎 (3房)
 $1449万
 $21,761/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -15073,7 +19449,7 @@
           <t>B | 382呎 (2房)
 $784万
 $20,526/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -15081,7 +19457,7 @@
           <t>C | 579呎 (3房)
 $1188万
 $20,527/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -15089,7 +19465,7 @@
           <t>D | 263呎 (1房)
 $467万
 $17,753/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -15097,7 +19473,7 @@
           <t>E | 383呎 (2房)
 $670万
 $17,507/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -15105,7 +19481,7 @@
           <t>F | 382呎 (2房)
 $656万
 $17,165/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -15113,7 +19489,7 @@
           <t>G | 395呎 (2房)
 $674万
 $17,068/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -15121,7 +19497,7 @@
           <t>H | 394呎 (2房)
 $659万
 $16,726/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -15129,7 +19505,7 @@
           <t>J | 261呎 (1房)
 $554万
 $21,245/呎
-(26年-06月)</t>
+(26年-06月-19日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -15137,7 +19513,7 @@
           <t>K | 260呎 (1房)
 $449万
 $17,262/呎
-(24年-08月)</t>
+(24年-08月-25日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -15145,7 +19521,7 @@
           <t>L | 390呎 (2房)
 $662万
 $16,985/呎
-(24年-09月)</t>
+(24年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -15160,7 +19536,7 @@
           <t>A | 666呎 (3房)
 $1383万
 $20,766/呎
-(24年-12月)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -15168,7 +19544,7 @@
           <t>B | 382呎 (2房)
 $813万
 $21,293/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -15176,7 +19552,7 @@
           <t>C | 579呎 (3房)
 $1183万
 $20,425/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -15184,7 +19560,7 @@
           <t>D | 263呎 (1房)
 $465万
 $17,696/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -15192,7 +19568,7 @@
           <t>E | 383呎 (2房)
 $671万
 $17,527/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -15200,7 +19576,7 @@
           <t>F | 382呎 (2房)
 $657万
 $17,188/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -15208,7 +19584,7 @@
           <t>G | 395呎 (2房)
 $672万
 $17,018/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -15216,7 +19592,7 @@
           <t>H | 394呎 (2房)
 $657万
 $16,678/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -15224,7 +19600,7 @@
           <t>J | 261呎 (1房)
 $435万
 $16,674/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -15232,7 +19608,7 @@
           <t>K | 260呎 (1房)
 $429万
 $16,504/呎
-(24年-08月)</t>
+(24年-08月-25日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -15240,7 +19616,7 @@
           <t>L | 390呎 (2房)
 $660万
 $16,931/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -15255,7 +19631,7 @@
           <t>A | 666呎 (3房)
 $1363万
 $20,470/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -15263,7 +19639,7 @@
           <t>B | 382呎 (2房)
 $776万
 $20,319/呎
-(24年-08月)</t>
+(24年-08月-18日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -15271,7 +19647,7 @@
           <t>C | 579呎 (3房)
 $1177万
 $20,323/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -15279,7 +19655,7 @@
           <t>D | 263呎 (1房)
 $464万
 $17,643/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -15287,7 +19663,7 @@
           <t>E | 383呎 (2房)
 $669万
 $17,475/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -15295,7 +19671,7 @@
           <t>F | 382呎 (2房)
 $655万
 $17,136/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -15303,7 +19679,7 @@
           <t>G | 395呎 (2房)
 $670万
 $16,967/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -15311,7 +19687,7 @@
           <t>H | 394呎 (2房)
 $642万
 $16,302/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -15319,7 +19695,7 @@
           <t>J | 261呎 (1房)
 $434万
 $16,625/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -15327,7 +19703,7 @@
           <t>K | 260呎 (1房)
 $427万
 $16,438/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -15335,7 +19711,7 @@
           <t>L | 390呎 (2房)
 $658万
 $16,882/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -15350,7 +19726,7 @@
           <t>A | 628呎 (3房)
 $1597万
 $25,428/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -15358,7 +19734,7 @@
           <t>B | 344呎 (2房)
 $739万
 $21,494/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -15366,7 +19742,7 @@
           <t>C | 579呎 (3房)
 $1158万
 $20,000/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -15374,7 +19750,7 @@
           <t>D | 263呎 (1房)
 $463万
 $17,589/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -15382,7 +19758,7 @@
           <t>E | 383呎 (2房)
 $654万
 $17,089/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -15390,7 +19766,7 @@
           <t>F | 382呎 (2房)
 $648万
 $16,969/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -15398,7 +19774,7 @@
           <t>G | 395呎 (2房)
 $643万
 $16,271/呎
-(25年-10月)</t>
+(25年-10月-26日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -15406,7 +19782,7 @@
           <t>H | 394呎 (2房)
 $640万
 $16,254/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -15414,7 +19790,7 @@
           <t>J | 224呎 (1房)
 $425万
 $18,960/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -15422,7 +19798,7 @@
           <t>K | 223呎 (1房)
 $438万
 $19,619/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -15430,7 +19806,7 @@
           <t>L | 390呎 (2房)
 $656万
 $16,831/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>150天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>150天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>150天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N155" s="3" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -17597,7 +17597,7 @@
           <t>H | 394呎 (2房)
 $746万
 $18,921/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -17605,7 +17605,7 @@
           <t>J | 261呎 (1房)
 $497万
 $19,042/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -17613,7 +17613,7 @@
           <t>K | 260呎 (1房)
 $499万
 $19,181/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -17660,7 +17660,7 @@
           <t>D | 263呎 (1房)
 $524万
 $19,909/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -17692,7 +17692,7 @@
           <t>H | 394呎 (2房)
 $738万
 $18,736/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -17700,7 +17700,7 @@
           <t>J | 261呎 (1房)
 $495万
 $18,966/呎
-(24年-09月)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -17708,7 +17708,7 @@
           <t>K | 260呎 (1房)
 $494万
 $18,988/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
@@ -17716,7 +17716,7 @@
           <t>L | 390呎 (2房)
 $716万
 $18,349/呎
-(24年-08月)</t>
+(24年-08月-18日)</t>
         </is>
       </c>
     </row>
@@ -17755,7 +17755,7 @@
           <t>D | 263呎 (1房)
 $519万
 $19,719/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -17787,7 +17787,7 @@
           <t>H | 394呎 (2房)
 $734万
 $18,642/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -17795,7 +17795,7 @@
           <t>J | 261呎 (1房)
 $496万
 $18,996/呎
-(24年-09月)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -17803,7 +17803,7 @@
           <t>K | 260呎 (1房)
 $486万
 $18,692/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -17811,7 +17811,7 @@
           <t>L | 390呎 (2房)
 $712万
 $18,259/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
           <t>D | 263呎 (1房)
 $511万
 $19,418/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -17858,7 +17858,7 @@
           <t>E | 383呎 (2房)
 $939万
 $24,520/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -17866,7 +17866,7 @@
           <t>F | 382呎 (2房)
 $871万
 $22,801/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -17874,7 +17874,7 @@
           <t>G | 395呎 (2房)
 $897万
 $22,701/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -17882,7 +17882,7 @@
           <t>H | 394呎 (2房)
 $731万
 $18,548/呎
-(24年-09月)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -17890,7 +17890,7 @@
           <t>J | 261呎 (1房)
 $493万
 $18,900/呎
-(24年-09月)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -17898,7 +17898,7 @@
           <t>K | 260呎 (1房)
 $484万
 $18,600/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -17906,7 +17906,7 @@
           <t>L | 390呎 (2房)
 $708万
 $18,167/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
           <t>D | 263呎 (1房)
 $506万
 $19,224/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -17953,7 +17953,7 @@
           <t>E | 383呎 (2房)
 $862万
 $22,496/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -17961,7 +17961,7 @@
           <t>F | 382呎 (2房)
 $843万
 $22,071/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -17969,7 +17969,7 @@
           <t>G | 395呎 (2房)
 $888万
 $22,476/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -17977,7 +17977,7 @@
           <t>H | 394呎 (2房)
 $727万
 $18,457/呎
-(24年-08月)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -17985,7 +17985,7 @@
           <t>J | 261呎 (1房)
 $491万
 $18,805/呎
-(24年-09月)</t>
+(24年-09月-08日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -17993,7 +17993,7 @@
           <t>K | 260呎 (1房)
 $481万
 $18,508/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
@@ -18001,7 +18001,7 @@
           <t>L | 390呎 (2房)
 $706万
 $18,113/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -18016,7 +18016,7 @@
           <t>A | 666呎 (3房)
 $1964万
 $29,488/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -18040,7 +18040,7 @@
           <t>D | 263呎 (1房)
 $503万
 $19,125/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -18048,7 +18048,7 @@
           <t>E | 383呎 (2房)
 $885万
 $23,110/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -18056,7 +18056,7 @@
           <t>F | 382呎 (2房)
 $842万
 $22,050/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -18064,7 +18064,7 @@
           <t>G | 395呎 (2房)
 $838万
 $21,203/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -18072,7 +18072,7 @@
           <t>H | 394呎 (2房)
 $725万
 $18,404/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -18080,7 +18080,7 @@
           <t>J | 261呎 (1房)
 $488万
 $18,713/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -18088,7 +18088,7 @@
           <t>K | 260呎 (1房)
 $499万
 $19,208/呎
-(24年-09月)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
@@ -18096,7 +18096,7 @@
           <t>L | 390呎 (2房)
 $704万
 $18,056/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -18127,7 +18127,7 @@
           <t>C | 579呎 (3房)
 $1514万
 $26,154/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -18135,7 +18135,7 @@
           <t>D | 263呎 (1房)
 $503万
 $19,137/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -18143,7 +18143,7 @@
           <t>E | 383呎 (2房)
 $812万
 $21,204/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -18151,7 +18151,7 @@
           <t>F | 382呎 (2房)
 $795万
 $20,801/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -18159,7 +18159,7 @@
           <t>G | 395呎 (2房)
 $813万
 $20,587/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -18167,7 +18167,7 @@
           <t>H | 394呎 (2房)
 $720万
 $18,277/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -18175,7 +18175,7 @@
           <t>J | 261呎 (1房)
 $486万
 $18,621/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -18183,7 +18183,7 @@
           <t>K | 260呎 (1房)
 $479万
 $18,427/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -18191,7 +18191,7 @@
           <t>L | 390呎 (2房)
 $732万
 $18,772/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
           <t>B | 382呎 (2房)
 $990万
 $25,919/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -18222,7 +18222,7 @@
           <t>C | 579呎 (3房)
 $1556万
 $26,870/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -18230,7 +18230,7 @@
           <t>D | 263呎 (1房)
 $498万
 $18,935/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -18238,7 +18238,7 @@
           <t>E | 383呎 (2房)
 $783万
 $20,446/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -18246,7 +18246,7 @@
           <t>F | 382呎 (2房)
 $769万
 $20,136/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -18254,7 +18254,7 @@
           <t>G | 395呎 (2房)
 $787万
 $19,929/呎
-(25年-10月)</t>
+(25年-10月-26日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -18262,7 +18262,7 @@
           <t>H | 394呎 (2房)
 $718万
 $18,221/呎
-(24年-10月)</t>
+(24年-10月-13日)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -18270,7 +18270,7 @@
           <t>J | 261呎 (1房)
 $484万
 $18,529/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -18278,7 +18278,7 @@
           <t>K | 260呎 (1房)
 $477万
 $18,338/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
@@ -18286,7 +18286,7 @@
           <t>L | 390呎 (2房)
 $747万
 $19,156/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
           <t>A | 666呎 (3房)
 $1698万
 $25,500/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -18317,7 +18317,7 @@
           <t>C | 579呎 (3房)
 $1427万
 $24,653/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -18325,7 +18325,7 @@
           <t>D | 263呎 (1房)
 $496万
 $18,840/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -18333,7 +18333,7 @@
           <t>E | 383呎 (2房)
 $763万
 $19,927/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -18341,7 +18341,7 @@
           <t>F | 382呎 (2房)
 $747万
 $19,550/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -18349,7 +18349,7 @@
           <t>G | 395呎 (2房)
 $764万
 $19,347/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -18357,7 +18357,7 @@
           <t>H | 394呎 (2房)
 $749万
 $19,015/呎
-(24年-08月)</t>
+(24年-08月-27日)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -18365,7 +18365,7 @@
           <t>J | 261呎 (1房)
 $502万
 $19,222/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -18373,7 +18373,7 @@
           <t>K | 260呎 (1房)
 $474万
 $18,246/呎
-(24年-09月)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr">
@@ -18381,7 +18381,7 @@
           <t>L | 390呎 (2房)
 $728万
 $18,662/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
           <t>A | 666呎 (3房)
 $1756万
 $26,362/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -18412,7 +18412,7 @@
           <t>C | 579呎 (3房)
 $1386万
 $23,934/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -18420,7 +18420,7 @@
           <t>D | 263呎 (1房)
 $496万
 $18,856/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -18428,7 +18428,7 @@
           <t>E | 383呎 (2房)
 $741万
 $19,347/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -18436,7 +18436,7 @@
           <t>F | 382呎 (2房)
 $725万
 $18,982/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -18444,7 +18444,7 @@
           <t>G | 395呎 (2房)
 $742万
 $18,787/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -18452,7 +18452,7 @@
           <t>H | 394呎 (2房)
 $716万
 $18,183/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -18460,7 +18460,7 @@
           <t>J | 261呎 (1房)
 $499万
 $19,126/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -18468,7 +18468,7 @@
           <t>K | 260呎 (1房)
 $600万
 $23,062/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
@@ -18476,7 +18476,7 @@
           <t>L | 390呎 (2房)
 $694万
 $17,800/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18491,7 @@
           <t>A | 666呎 (3房)
 $1626万
 $24,410/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -18499,7 +18499,7 @@
           <t>B | 382呎 (2房)
 $947万
 $24,788/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -18507,7 +18507,7 @@
           <t>C | 579呎 (3房)
 $1352万
 $23,349/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -18515,7 +18515,7 @@
           <t>D | 263呎 (1房)
 $490万
 $18,650/呎
-(24年-10月)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -18523,7 +18523,7 @@
           <t>E | 383呎 (2房)
 $703万
 $18,350/呎
-(24年-10月)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -18531,7 +18531,7 @@
           <t>F | 382呎 (2房)
 $717万
 $18,772/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -18539,7 +18539,7 @@
           <t>G | 395呎 (2房)
 $704万
 $17,818/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -18547,7 +18547,7 @@
           <t>H | 394呎 (2房)
 $745万
 $18,901/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -18555,7 +18555,7 @@
           <t>J | 261呎 (1房)
 $476万
 $18,253/呎
-(25年-02月)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -18563,7 +18563,7 @@
           <t>K | 260呎 (1房)
 $470万
 $18,065/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -18571,7 +18571,7 @@
           <t>L | 390呎 (2房)
 $687万
 $17,623/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -18586,7 +18586,7 @@
           <t>A | 666呎 (3房)
 $1594万
 $23,932/呎
-(26年-02月)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -18594,7 +18594,7 @@
           <t>B | 382呎 (2房)
 $906万
 $23,720/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -18602,7 +18602,7 @@
           <t>C | 579呎 (3房)
 $1332万
 $23,005/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -18610,7 +18610,7 @@
           <t>D | 263呎 (1房)
 $488万
 $18,559/呎
-(24年-10月)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -18618,7 +18618,7 @@
           <t>E | 383呎 (2房)
 $699万
 $18,261/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -18626,7 +18626,7 @@
           <t>F | 382呎 (2房)
 $684万
 $17,914/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -18634,7 +18634,7 @@
           <t>G | 395呎 (2房)
 $700万
 $17,729/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -18642,7 +18642,7 @@
           <t>H | 394呎 (2房)
 $712万
 $18,074/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -18650,7 +18650,7 @@
           <t>J | 261呎 (1房)
 $472万
 $18,073/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -18658,7 +18658,7 @@
           <t>K | 260呎 (1房)
 $465万
 $17,885/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -18666,7 +18666,7 @@
           <t>L | 390呎 (2房)
 $710万
 $18,195/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
           <t>A | 666呎 (3房)
 $1563万
 $23,462/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -18689,7 +18689,7 @@
           <t>B | 382呎 (2房)
 $867万
 $22,696/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -18697,7 +18697,7 @@
           <t>C | 579呎 (3房)
 $1312万
 $22,665/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -18705,7 +18705,7 @@
           <t>D | 263呎 (1房)
 $486万
 $18,464/呎
-(24年-10月)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -18713,7 +18713,7 @@
           <t>E | 383呎 (2房)
 $696万
 $18,170/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -18721,7 +18721,7 @@
           <t>F | 382呎 (2房)
 $681万
 $17,825/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -18729,7 +18729,7 @@
           <t>G | 395呎 (2房)
 $697万
 $17,641/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -18737,7 +18737,7 @@
           <t>H | 394呎 (2房)
 $710万
 $18,020/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -18745,7 +18745,7 @@
           <t>J | 261呎 (1房)
 $470万
 $18,019/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -18753,7 +18753,7 @@
           <t>K | 260呎 (1房)
 $464万
 $17,831/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -18761,7 +18761,7 @@
           <t>L | 390呎 (2房)
 $678万
 $17,397/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -18776,7 +18776,7 @@
           <t>A | 666呎 (3房)
 $1532万
 $23,002/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -18792,7 +18792,7 @@
           <t>C | 579呎 (3房)
 $1247万
 $21,537/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -18800,7 +18800,7 @@
           <t>D | 263呎 (1房)
 $480万
 $18,232/呎
-(24年-08月)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -18808,7 +18808,7 @@
           <t>E | 383呎 (2房)
 $692万
 $18,063/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -18816,7 +18816,7 @@
           <t>F | 382呎 (2房)
 $677万
 $17,712/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -18824,7 +18824,7 @@
           <t>G | 395呎 (2房)
 $693万
 $17,537/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -18832,7 +18832,7 @@
           <t>H | 394呎 (2房)
 $708万
 $17,967/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -18840,7 +18840,7 @@
           <t>J | 261呎 (1房)
 $469万
 $17,966/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -18848,7 +18848,7 @@
           <t>K | 260呎 (1房)
 $462万
 $17,781/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -18856,7 +18856,7 @@
           <t>L | 390呎 (2房)
 $705万
 $18,087/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -18871,7 +18871,7 @@
           <t>A | 666呎 (3房)
 $1502万
 $22,550/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -18879,7 +18879,7 @@
           <t>B | 382呎 (2房)
 $838万
 $21,924/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -18887,7 +18887,7 @@
           <t>C | 579呎 (3房)
 $1239万
 $21,404/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -18895,7 +18895,7 @@
           <t>D | 263呎 (1房)
 $477万
 $18,144/呎
-(24年-09月)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -18903,7 +18903,7 @@
           <t>E | 383呎 (2房)
 $688万
 $17,971/呎
-(24年-09月)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -18911,7 +18911,7 @@
           <t>F | 382呎 (2房)
 $673万
 $17,623/呎
-(24年-08月)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -18919,7 +18919,7 @@
           <t>G | 395呎 (2房)
 $686万
 $17,377/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -18927,7 +18927,7 @@
           <t>H | 394呎 (2房)
 $706万
 $17,911/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -18935,7 +18935,7 @@
           <t>J | 261呎 (1房)
 $468万
 $17,912/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -18943,7 +18943,7 @@
           <t>K | 260呎 (1房)
 $461万
 $17,727/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -18951,7 +18951,7 @@
           <t>L | 390呎 (2房)
 $674万
 $17,290/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -18966,7 +18966,7 @@
           <t>A | 666呎 (3房)
 $1470万
 $22,069/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -18974,7 +18974,7 @@
           <t>B | 382呎 (2房)
 $812万
 $21,254/呎
-(24年-08月)</t>
+(24年-08月-18日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -18982,7 +18982,7 @@
           <t>C | 579呎 (3房)
 $1218万
 $21,033/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -18990,7 +18990,7 @@
           <t>D | 263呎 (1房)
 $475万
 $18,053/呎
-(24年-09月)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -18998,7 +18998,7 @@
           <t>E | 383呎 (2房)
 $685万
 $17,883/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -19006,7 +19006,7 @@
           <t>F | 382呎 (2房)
 $670万
 $17,534/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -19014,7 +19014,7 @@
           <t>G | 395呎 (2房)
 $686万
 $17,362/呎
-(24年-09月)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -19022,7 +19022,7 @@
           <t>H | 394呎 (2房)
 $692万
 $17,561/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -19030,7 +19030,7 @@
           <t>J | 261呎 (1房)
 $458万
 $17,559/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -19038,7 +19038,7 @@
           <t>K | 260呎 (1房)
 $452万
 $17,381/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -19046,7 +19046,7 @@
           <t>L | 390呎 (2房)
 $670万
 $17,169/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -19061,7 +19061,7 @@
           <t>A | 666呎 (3房)
 $1461万
 $21,932/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -19069,7 +19069,7 @@
           <t>B | 382呎 (2房)
 $808万
 $21,147/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -19077,7 +19077,7 @@
           <t>C | 579呎 (3房)
 $1224万
 $21,149/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -19085,7 +19085,7 @@
           <t>D | 263呎 (1房)
 $472万
 $17,966/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -19093,7 +19093,7 @@
           <t>E | 383呎 (2房)
 $682万
 $17,794/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -19101,7 +19101,7 @@
           <t>F | 382呎 (2房)
 $666万
 $17,448/呎
-(24年-08月)</t>
+(24年-08月-18日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -19109,7 +19109,7 @@
           <t>G | 395呎 (2房)
 $712万
 $18,015/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -19117,7 +19117,7 @@
           <t>H | 394呎 (2房)
 $707万
 $17,954/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -19125,7 +19125,7 @@
           <t>J | 261呎 (1房)
 $468万
 $17,946/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -19133,7 +19133,7 @@
           <t>K | 260呎 (1房)
 $443万
 $17,038/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -19141,7 +19141,7 @@
           <t>L | 390呎 (2房)
 $670万
 $17,187/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
           <t>A | 666呎 (3房)
 $1426万
 $21,416/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -19164,7 +19164,7 @@
           <t>B | 382呎 (2房)
 $838万
 $21,940/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -19172,7 +19172,7 @@
           <t>C | 579呎 (3房)
 $1216万
 $20,997/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -19180,7 +19180,7 @@
           <t>D | 263呎 (1房)
 $598万
 $22,745/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -19188,7 +19188,7 @@
           <t>E | 383呎 (2房)
 $680万
 $17,742/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -19196,7 +19196,7 @@
           <t>F | 382呎 (2房)
 $693万
 $18,136/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -19204,7 +19204,7 @@
           <t>G | 395呎 (2房)
 $680万
 $17,223/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -19212,7 +19212,7 @@
           <t>H | 394呎 (2房)
 $665万
 $16,878/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -19220,7 +19220,7 @@
           <t>J | 261呎 (1房)
 $440万
 $16,877/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -19228,7 +19228,7 @@
           <t>K | 260呎 (1房)
 $453万
 $17,415/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
@@ -19251,7 +19251,7 @@
           <t>A | 666呎 (3房)
 $1418万
 $21,288/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19259,7 +19259,7 @@
           <t>B | 382呎 (2房)
 $800万
 $20,937/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -19267,7 +19267,7 @@
           <t>C | 579呎 (3房)
 $1212万
 $20,940/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -19275,7 +19275,7 @@
           <t>D | 263呎 (1房)
 $470万
 $17,856/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -19283,7 +19283,7 @@
           <t>E | 383呎 (2房)
 $706万
 $18,444/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -19291,7 +19291,7 @@
           <t>F | 382呎 (2房)
 $663万
 $17,346/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -19299,7 +19299,7 @@
           <t>G | 395呎 (2房)
 $676万
 $17,101/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -19307,7 +19307,7 @@
           <t>H | 394呎 (2房)
 $663万
 $16,830/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -19315,7 +19315,7 @@
           <t>J | 261呎 (1房)
 $439万
 $16,828/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -19323,7 +19323,7 @@
           <t>K | 260呎 (1房)
 $433万
 $16,654/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -19331,7 +19331,7 @@
           <t>L | 390呎 (2房)
 $666万
 $17,087/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -19346,7 +19346,7 @@
           <t>A | 666呎 (3房)
 $1464万
 $21,977/呎
-(24年-08月)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -19354,7 +19354,7 @@
           <t>B | 382呎 (2房)
 $792万
 $20,730/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -19362,7 +19362,7 @@
           <t>C | 579呎 (3房)
 $1200万
 $20,731/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -19370,7 +19370,7 @@
           <t>D | 263呎 (1房)
 $488万
 $18,567/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -19378,7 +19378,7 @@
           <t>E | 383呎 (2房)
 $675万
 $17,632/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -19386,7 +19386,7 @@
           <t>F | 382呎 (2房)
 $660万
 $17,291/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -19394,7 +19394,7 @@
           <t>G | 395呎 (2房)
 $674万
 $17,051/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -19402,7 +19402,7 @@
           <t>H | 394呎 (2房)
 $661万
 $16,779/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -19410,7 +19410,7 @@
           <t>J | 261呎 (1房)
 $438万
 $16,778/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -19418,7 +19418,7 @@
           <t>K | 260呎 (1房)
 $432万
 $16,604/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -19426,7 +19426,7 @@
           <t>L | 390呎 (2房)
 $664万
 $17,036/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -19441,7 +19441,7 @@
           <t>A | 666呎 (3房)
 $1449万
 $21,761/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -19449,7 +19449,7 @@
           <t>B | 382呎 (2房)
 $784万
 $20,526/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -19457,7 +19457,7 @@
           <t>C | 579呎 (3房)
 $1188万
 $20,527/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -19465,7 +19465,7 @@
           <t>D | 263呎 (1房)
 $467万
 $17,753/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -19473,7 +19473,7 @@
           <t>E | 383呎 (2房)
 $670万
 $17,507/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -19481,7 +19481,7 @@
           <t>F | 382呎 (2房)
 $656万
 $17,165/呎
-(24年-10月)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -19489,7 +19489,7 @@
           <t>G | 395呎 (2房)
 $674万
 $17,068/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -19497,7 +19497,7 @@
           <t>H | 394呎 (2房)
 $659万
 $16,726/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -19505,7 +19505,7 @@
           <t>J | 261呎 (1房)
 $554万
 $21,245/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -19513,7 +19513,7 @@
           <t>K | 260呎 (1房)
 $449万
 $17,262/呎
-(24年-08月)</t>
+(24年-08月-25日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -19521,7 +19521,7 @@
           <t>L | 390呎 (2房)
 $662万
 $16,985/呎
-(24年-09月)</t>
+(24年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -19536,7 +19536,7 @@
           <t>A | 666呎 (3房)
 $1383万
 $20,766/呎
-(24年-12月)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -19544,7 +19544,7 @@
           <t>B | 382呎 (2房)
 $813万
 $21,293/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -19552,7 +19552,7 @@
           <t>C | 579呎 (3房)
 $1183万
 $20,425/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -19560,7 +19560,7 @@
           <t>D | 263呎 (1房)
 $465万
 $17,696/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -19568,7 +19568,7 @@
           <t>E | 383呎 (2房)
 $671万
 $17,527/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -19576,7 +19576,7 @@
           <t>F | 382呎 (2房)
 $657万
 $17,188/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -19584,7 +19584,7 @@
           <t>G | 395呎 (2房)
 $672万
 $17,018/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -19592,7 +19592,7 @@
           <t>H | 394呎 (2房)
 $657万
 $16,678/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -19600,7 +19600,7 @@
           <t>J | 261呎 (1房)
 $435万
 $16,674/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -19608,7 +19608,7 @@
           <t>K | 260呎 (1房)
 $429万
 $16,504/呎
-(24年-08月)</t>
+(24年-08月-25日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -19616,7 +19616,7 @@
           <t>L | 390呎 (2房)
 $660万
 $16,931/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -19631,7 +19631,7 @@
           <t>A | 666呎 (3房)
 $1363万
 $20,470/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -19639,7 +19639,7 @@
           <t>B | 382呎 (2房)
 $776万
 $20,319/呎
-(24年-08月)</t>
+(24年-08月-18日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -19647,7 +19647,7 @@
           <t>C | 579呎 (3房)
 $1177万
 $20,323/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -19655,7 +19655,7 @@
           <t>D | 263呎 (1房)
 $464万
 $17,643/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -19663,7 +19663,7 @@
           <t>E | 383呎 (2房)
 $669万
 $17,475/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -19671,7 +19671,7 @@
           <t>F | 382呎 (2房)
 $655万
 $17,136/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -19679,7 +19679,7 @@
           <t>G | 395呎 (2房)
 $670万
 $16,967/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -19687,7 +19687,7 @@
           <t>H | 394呎 (2房)
 $642万
 $16,302/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -19695,7 +19695,7 @@
           <t>J | 261呎 (1房)
 $434万
 $16,625/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -19703,7 +19703,7 @@
           <t>K | 260呎 (1房)
 $427万
 $16,438/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -19711,7 +19711,7 @@
           <t>L | 390呎 (2房)
 $658万
 $16,882/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -19726,7 +19726,7 @@
           <t>A | 628呎 (3房)
 $1597万
 $25,428/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -19734,7 +19734,7 @@
           <t>B | 344呎 (2房)
 $739万
 $21,494/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -19742,7 +19742,7 @@
           <t>C | 579呎 (3房)
 $1158万
 $20,000/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -19750,7 +19750,7 @@
           <t>D | 263呎 (1房)
 $463万
 $17,589/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -19758,7 +19758,7 @@
           <t>E | 383呎 (2房)
 $654万
 $17,089/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -19766,7 +19766,7 @@
           <t>F | 382呎 (2房)
 $648万
 $16,969/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -19774,7 +19774,7 @@
           <t>G | 395呎 (2房)
 $643万
 $16,271/呎
-(25年-10月)</t>
+(25年-10月-26日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -19782,7 +19782,7 @@
           <t>H | 394呎 (2房)
 $640万
 $16,254/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -19790,7 +19790,7 @@
           <t>J | 224呎 (1房)
 $425万
 $18,960/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -19798,7 +19798,7 @@
           <t>K | 223呎 (1房)
 $438万
 $19,619/呎
-(24年-08月)</t>
+(24年-08月-15日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -19806,7 +19806,7 @@
           <t>L | 390呎 (2房)
 $656万
 $16,831/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
